--- a/artfynd/A 68622-2021 artfynd.xlsx
+++ b/artfynd/A 68622-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3268,6 +3268,103 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126571915</v>
+      </c>
+      <c r="B23" t="n">
+        <v>56584</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hova, Hova, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>415510</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6575157</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Maria Ahlefelt</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Maria Ahlefelt</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 68622-2021 artfynd.xlsx
+++ b/artfynd/A 68622-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>114980208</v>
       </c>
       <c r="B2" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,59 +784,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116435895</v>
+        <v>119029111</v>
       </c>
       <c r="B3" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>101735</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>415278</v>
+        <v>415259</v>
       </c>
       <c r="R3" t="n">
-        <v>6575170</v>
+        <v>6575189</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,29 +849,34 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Eventuellt spår av jättesvampmal i fnöskticka på björklåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -910,56 +896,56 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116434762</v>
+        <v>119028323</v>
       </c>
       <c r="B4" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>415081</v>
+        <v>415252</v>
       </c>
       <c r="R4" t="n">
         <v>6575168</v>
@@ -989,27 +975,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ca 25 st inom en yta på 4m2.</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,59 +1017,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116435766</v>
+        <v>119028332</v>
       </c>
       <c r="B5" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>415246</v>
+        <v>415263</v>
       </c>
       <c r="R5" t="n">
-        <v>6575172</v>
+        <v>6575176</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,22 +1096,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,59 +1138,59 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116435535</v>
+        <v>119028761</v>
       </c>
       <c r="B6" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>415243</v>
+        <v>415236</v>
       </c>
       <c r="R6" t="n">
-        <v>6575173</v>
+        <v>6575165</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,22 +1217,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,15 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119028323</v>
+        <v>119029151</v>
       </c>
       <c r="B7" t="n">
-        <v>58136</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,14 +1304,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>415252</v>
+        <v>415247</v>
       </c>
       <c r="R7" t="n">
-        <v>6575168</v>
+        <v>6575194</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1367,7 +1343,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1377,7 +1353,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,64 +1380,59 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119028062</v>
+        <v>119029385</v>
       </c>
       <c r="B8" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>415071</v>
+        <v>415155</v>
       </c>
       <c r="R8" t="n">
-        <v>6575189</v>
+        <v>6575245</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1493,7 +1464,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1503,12 +1474,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Precis intill stigen.</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1535,15 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119029111</v>
+        <v>119029519</v>
       </c>
       <c r="B9" t="n">
-        <v>43675</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,34 +1512,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101735</v>
+        <v>208245</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>415259</v>
+        <v>415163</v>
       </c>
       <c r="R9" t="n">
-        <v>6575189</v>
+        <v>6575274</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1608,31 +1583,16 @@
           <t>2024-08-10</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-10</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Eventuellt spår av jättesvampmal i fnöskticka på björklåga</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
@@ -1652,15 +1612,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119028332</v>
+        <v>119029850</v>
       </c>
       <c r="B10" t="n">
-        <v>58136</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1702,14 +1657,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>415263</v>
+        <v>415293</v>
       </c>
       <c r="R10" t="n">
-        <v>6575176</v>
+        <v>6575221</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1741,7 +1696,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1751,7 +1706,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1778,15 +1733,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119028761</v>
+        <v>119030007</v>
       </c>
       <c r="B11" t="n">
-        <v>58136</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,21 +1744,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208245</v>
+        <v>208249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1823,19 +1773,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>415236</v>
+        <v>415320</v>
       </c>
       <c r="R11" t="n">
-        <v>6575165</v>
+        <v>6575199</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1867,7 +1817,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1877,7 +1827,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1904,15 +1854,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119030007</v>
+        <v>119028394</v>
       </c>
       <c r="B12" t="n">
-        <v>58164</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58815</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,21 +1865,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208249</v>
+        <v>208250</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1949,16 +1894,19 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>415320</v>
+        <v>415257</v>
       </c>
       <c r="R12" t="n">
         <v>6575199</v>
@@ -1993,7 +1941,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2003,7 +1951,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2012,6 +1960,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2030,53 +1979,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119028827</v>
+        <v>126571915</v>
       </c>
       <c r="B13" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56876</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>208257</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Hova, Hova, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>415244</v>
+        <v>415510</v>
       </c>
       <c r="R13" t="n">
-        <v>6575232</v>
+        <v>6575157</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2100,27 +2044,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Nära en liten nedfallen gran, se bild</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2135,27 +2064,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Åsa Duell</t>
+          <t>Maria Ahlefelt</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Åsa Duell</t>
+          <t>Maria Ahlefelt</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119028980</v>
+        <v>116434762</v>
       </c>
       <c r="B14" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,7 +2106,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2192,14 +2116,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>415264</v>
+        <v>415081</v>
       </c>
       <c r="R14" t="n">
-        <v>6575153</v>
+        <v>6575168</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2226,22 +2150,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ca 25 st inom en yta på 4m2.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2268,15 +2197,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119029491</v>
+        <v>116435535</v>
       </c>
       <c r="B15" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2303,7 +2227,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2313,14 +2237,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>415172</v>
+        <v>415243</v>
       </c>
       <c r="R15" t="n">
-        <v>6575265</v>
+        <v>6575173</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2347,27 +2271,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Vid foten av en björk, se bild.</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2394,64 +2313,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119029151</v>
+        <v>116435698</v>
       </c>
       <c r="B16" t="n">
-        <v>58136</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208245</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>415247</v>
+        <v>415246</v>
       </c>
       <c r="R16" t="n">
-        <v>6575194</v>
+        <v>6575172</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2478,22 +2382,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2502,6 +2406,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2520,64 +2425,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119029850</v>
+        <v>116435895</v>
       </c>
       <c r="B17" t="n">
-        <v>58136</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>208245</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>årsunge</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>415293</v>
+        <v>415278</v>
       </c>
       <c r="R17" t="n">
-        <v>6575221</v>
+        <v>6575170</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2604,22 +2499,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2646,64 +2541,59 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119029385</v>
+        <v>119027915</v>
       </c>
       <c r="B18" t="n">
-        <v>58136</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>208245</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>415155</v>
+        <v>415071</v>
       </c>
       <c r="R18" t="n">
-        <v>6575245</v>
+        <v>6575193</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2735,7 +2625,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2745,7 +2635,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2772,15 +2662,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119027915</v>
+        <v>119028062</v>
       </c>
       <c r="B19" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2807,29 +2692,29 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
         <v>415071</v>
       </c>
       <c r="R19" t="n">
-        <v>6575193</v>
+        <v>6575189</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2861,7 +2746,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2871,7 +2756,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Precis intill stigen.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2901,12 +2791,7 @@
         <v>119028529</v>
       </c>
       <c r="B20" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2943,7 +2828,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
@@ -3024,64 +2909,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119029519</v>
+        <v>119028827</v>
       </c>
       <c r="B21" t="n">
-        <v>58136</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>208245</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>415163</v>
+        <v>415244</v>
       </c>
       <c r="R21" t="n">
-        <v>6575274</v>
+        <v>6575232</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3111,9 +2977,24 @@
           <t>2024-08-10</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-10</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Nära en liten nedfallen gran, se bild</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3140,67 +3021,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119028394</v>
+        <v>119028980</v>
       </c>
       <c r="B22" t="n">
-        <v>58162</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>208250</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Eludden, Hammarö  (Eludden, Hammarö ), Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>415257</v>
+        <v>415264</v>
       </c>
       <c r="R22" t="n">
-        <v>6575199</v>
+        <v>6575153</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3232,7 +3100,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3242,7 +3110,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3251,7 +3119,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3270,48 +3137,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126571915</v>
+        <v>119029491</v>
       </c>
       <c r="B23" t="n">
-        <v>56584</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>208257</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hova, Hova, Vrm</t>
+          <t>Eludden, Hammarö , Eludden, Hammarö , Vrm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>415510</v>
+        <v>415172</v>
       </c>
       <c r="R23" t="n">
-        <v>6575157</v>
+        <v>6575265</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3335,12 +3211,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-08-10</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-08-10</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Vid foten av en björk, se bild.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3355,12 +3246,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Maria Ahlefelt</t>
+          <t>Åsa Duell</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Maria Ahlefelt</t>
+          <t>Åsa Duell</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 68622-2021 artfynd.xlsx
+++ b/artfynd/A 68622-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114980208</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119029111</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119028323</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,6 +1155,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119028332</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1256,6 +1281,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119028761</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1377,6 +1407,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119029151</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1498,6 +1533,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119029385</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1609,6 +1649,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119029519</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1730,6 +1775,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119029850</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1851,6 +1901,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119030007</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1976,6 +2031,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119028394</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2073,6 +2133,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126571915</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2194,6 +2259,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116434762</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2310,6 +2380,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116435535</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2422,6 +2497,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116435698</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2538,6 +2618,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116435895</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2659,6 +2744,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119027915</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2785,6 +2875,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119028062</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2906,6 +3001,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119028529</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3018,6 +3118,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119028827</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3134,6 +3239,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119028980</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3255,8 +3365,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119029491</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>